--- a/src/data/menus.xlsx
+++ b/src/data/menus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857A8F04-7AFB-46E6-B33F-6940DCD7DFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE83D40-46C6-4D4D-B279-80CA5FCB7665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,43 +39,625 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="204">
   <si>
     <t>Menu Location</t>
   </si>
   <si>
-    <t xml:space="preserve"> Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URL / Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Parent Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sort Order</t>
-  </si>
-  <si>
-    <t>header</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
-    <t>/index.html</t>
-  </si>
-  <si>
     <t>_self</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>URL / Link</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Parent Item</t>
+  </si>
+  <si>
+    <t>Sort Order</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>(None)</t>
+  </si>
+  <si>
+    <t>Power Tools</t>
+  </si>
+  <si>
+    <t>/power-tools</t>
+  </si>
+  <si>
+    <t>Hand Tools</t>
+  </si>
+  <si>
+    <t>/hand-tools</t>
+  </si>
+  <si>
+    <t>Car Care Products</t>
+  </si>
+  <si>
+    <t>/car-care-products</t>
+  </si>
+  <si>
+    <t>Solar Panels &amp; Systems</t>
+  </si>
+  <si>
+    <t>/solar-panels-systems</t>
+  </si>
+  <si>
+    <t>Brands</t>
+  </si>
+  <si>
+    <t>/brands</t>
+  </si>
+  <si>
+    <t>Cordless Tools</t>
+  </si>
+  <si>
+    <t>/cordless-tools</t>
+  </si>
+  <si>
+    <t>Cutting &amp; Abrasive Tools</t>
+  </si>
+  <si>
+    <t>/cutting-abrasive-tools</t>
+  </si>
+  <si>
+    <t>Workshop Equipment</t>
+  </si>
+  <si>
+    <t>/workshop-equipment</t>
+  </si>
+  <si>
+    <t>Solar Inverters &amp; Batteries</t>
+  </si>
+  <si>
+    <t>/solar-inverters-batteries</t>
+  </si>
+  <si>
+    <t>Footer Menu</t>
+  </si>
+  <si>
+    <t>About Us</t>
+  </si>
+  <si>
+    <t>/about-us</t>
+  </si>
+  <si>
+    <t>Contact Us</t>
+  </si>
+  <si>
+    <t>/contact-us</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>/privacy-policy</t>
+  </si>
+  <si>
+    <t>Terms &amp; Conditions</t>
+  </si>
+  <si>
+    <t>/terms-conditions</t>
+  </si>
+  <si>
+    <t>Bosch</t>
+  </si>
+  <si>
+    <t>/brand/bosch</t>
+  </si>
+  <si>
+    <t>INGCO</t>
+  </si>
+  <si>
+    <t>/brand/ingco</t>
+  </si>
+  <si>
+    <t>Makita</t>
+  </si>
+  <si>
+    <t>/brand/makita</t>
+  </si>
+  <si>
+    <t>DeWalt</t>
+  </si>
+  <si>
+    <t>/brand/dewalt</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>/brand/stanley</t>
+  </si>
+  <si>
+    <t>Taparia</t>
+  </si>
+  <si>
+    <t>/brand/taparia</t>
+  </si>
+  <si>
+    <t>Tata Solar</t>
+  </si>
+  <si>
+    <t>/brand/tata-solar</t>
+  </si>
+  <si>
+    <t>Adani Solar</t>
+  </si>
+  <si>
+    <t>/brand/adani-solar</t>
+  </si>
+  <si>
+    <t>Luminous</t>
+  </si>
+  <si>
+    <t>/brand/luminous</t>
+  </si>
+  <si>
+    <t>WaveX</t>
+  </si>
+  <si>
+    <t>/brand/wavex</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>/brand/milwaukee</t>
+  </si>
+  <si>
+    <t>Dongcheng</t>
+  </si>
+  <si>
+    <t>/brand/dongcheng</t>
+  </si>
+  <si>
+    <t>Ryobi</t>
+  </si>
+  <si>
+    <t>/brand/ryobi</t>
+  </si>
+  <si>
+    <t>SKIL</t>
+  </si>
+  <si>
+    <t>/brand/skil</t>
+  </si>
+  <si>
+    <t>Stihl</t>
+  </si>
+  <si>
+    <t>/brand/stihl</t>
+  </si>
+  <si>
+    <t>Groz</t>
+  </si>
+  <si>
+    <t>/brand/groz</t>
+  </si>
+  <si>
+    <t>CUMI</t>
+  </si>
+  <si>
+    <t>/brand/cumi</t>
+  </si>
+  <si>
+    <t>Sonax</t>
+  </si>
+  <si>
+    <t>/brand/sonax</t>
+  </si>
+  <si>
+    <t>Loom Solar</t>
+  </si>
+  <si>
+    <t>/brand/loom-solar</t>
+  </si>
+  <si>
+    <t>Microtek</t>
+  </si>
+  <si>
+    <t>/brand/microtek</t>
+  </si>
+  <si>
+    <t>Eastman</t>
+  </si>
+  <si>
+    <t>/brand/eastman</t>
+  </si>
+  <si>
+    <t>Xtra Power</t>
+  </si>
+  <si>
+    <t>/brand/xtra-power</t>
+  </si>
+  <si>
+    <t>Hilti</t>
+  </si>
+  <si>
+    <t>/brand/hilti</t>
+  </si>
+  <si>
+    <t>Festool</t>
+  </si>
+  <si>
+    <t>/brand/festool</t>
+  </si>
+  <si>
+    <t>Dremel</t>
+  </si>
+  <si>
+    <t>/brand/dremel</t>
+  </si>
+  <si>
+    <t>Freemans</t>
+  </si>
+  <si>
+    <t>/brand/freemans</t>
+  </si>
+  <si>
+    <t>Waaree Solar</t>
+  </si>
+  <si>
+    <t>/brand/waaree-solar</t>
+  </si>
+  <si>
+    <t>Vikram Solar</t>
+  </si>
+  <si>
+    <t>/brand/vikram-solar</t>
+  </si>
+  <si>
+    <t>Exide Solar</t>
+  </si>
+  <si>
+    <t>/brand/exide-solar</t>
+  </si>
+  <si>
+    <t>UTL</t>
+  </si>
+  <si>
+    <t>/brand/utl</t>
+  </si>
+  <si>
+    <t>Metabo</t>
+  </si>
+  <si>
+    <t>/brand/metabo</t>
+  </si>
+  <si>
+    <t>Black + Decker</t>
+  </si>
+  <si>
+    <t>/brand/black-decker</t>
+  </si>
+  <si>
+    <t>HiKOKI</t>
+  </si>
+  <si>
+    <t>/brand/hikoki</t>
+  </si>
+  <si>
+    <t>Formula 1</t>
+  </si>
+  <si>
+    <t>/brand/formula-1</t>
+  </si>
+  <si>
+    <t>3M Auto</t>
+  </si>
+  <si>
+    <t>/brand/3m-auto</t>
+  </si>
+  <si>
+    <t>Meguiar's</t>
+  </si>
+  <si>
+    <t>/brand/meguiars</t>
+  </si>
+  <si>
+    <t>Turtle Wax</t>
+  </si>
+  <si>
+    <t>/brand/turtle-wax</t>
+  </si>
+  <si>
+    <t>Kenbrook</t>
+  </si>
+  <si>
+    <t>/brand/kenbrook</t>
+  </si>
+  <si>
+    <t>Fujiyama</t>
+  </si>
+  <si>
+    <t>/brand/fujiyama</t>
+  </si>
+  <si>
+    <t>Shakti</t>
+  </si>
+  <si>
+    <t>/brand/shakti</t>
+  </si>
+  <si>
+    <t>JRS Drive</t>
+  </si>
+  <si>
+    <t>/brand/jrs-drive</t>
+  </si>
+  <si>
+    <t>Camron Pro</t>
+  </si>
+  <si>
+    <t>/brand/camron-pro</t>
+  </si>
+  <si>
+    <t>Torque Master</t>
+  </si>
+  <si>
+    <t>/brand/torque-master</t>
+  </si>
+  <si>
+    <t>Carbiforce</t>
+  </si>
+  <si>
+    <t>/brand/carbiforce</t>
+  </si>
+  <si>
+    <t>Delta UPS</t>
+  </si>
+  <si>
+    <t>/brand/delta-ups</t>
+  </si>
+  <si>
+    <t>Powertuff</t>
+  </si>
+  <si>
+    <t>/brand/powertuff</t>
+  </si>
+  <si>
+    <t>OMXE</t>
+  </si>
+  <si>
+    <t>/brand/omxe</t>
+  </si>
+  <si>
+    <t>MultiTec</t>
+  </si>
+  <si>
+    <t>/brand/multitec</t>
+  </si>
+  <si>
+    <t>Metaldur</t>
+  </si>
+  <si>
+    <t>/brand/metaldur</t>
+  </si>
+  <si>
+    <t>Mac Master</t>
+  </si>
+  <si>
+    <t>/brand/mac-master</t>
+  </si>
+  <si>
+    <t>9JackTools</t>
+  </si>
+  <si>
+    <t>/brand/9jacktools</t>
+  </si>
+  <si>
+    <t>Xcel</t>
+  </si>
+  <si>
+    <t>/brand/xcel</t>
+  </si>
+  <si>
+    <t>Kinee Solar</t>
+  </si>
+  <si>
+    <t>/brand/kinee-solar</t>
+  </si>
+  <si>
+    <t>Ukava</t>
+  </si>
+  <si>
+    <t>/brand/ukava</t>
+  </si>
+  <si>
+    <t>DCA</t>
+  </si>
+  <si>
+    <t>/brand/dca</t>
+  </si>
+  <si>
+    <t>Chemical Guys</t>
+  </si>
+  <si>
+    <t>/brand/chemical-guys</t>
+  </si>
+  <si>
+    <t>Waxpol</t>
+  </si>
+  <si>
+    <t>/brand/waxpol</t>
+  </si>
+  <si>
+    <t>Mothers</t>
+  </si>
+  <si>
+    <t>/brand/mothers</t>
+  </si>
+  <si>
+    <t>ShineXpro</t>
+  </si>
+  <si>
+    <t>/brand/shinexpro</t>
+  </si>
+  <si>
+    <t>Goldi Solar</t>
+  </si>
+  <si>
+    <t>/brand/goldi-solar</t>
+  </si>
+  <si>
+    <t>Premier Energies</t>
+  </si>
+  <si>
+    <t>/brand/premier-energies</t>
+  </si>
+  <si>
+    <t>Havells</t>
+  </si>
+  <si>
+    <t>/brand/havells</t>
+  </si>
+  <si>
+    <t>Servotech</t>
+  </si>
+  <si>
+    <t>/brand/servotech</t>
+  </si>
+  <si>
+    <t>Su-Kam</t>
+  </si>
+  <si>
+    <t>/brand/su-kam</t>
+  </si>
+  <si>
+    <t>Krost</t>
+  </si>
+  <si>
+    <t>/brand/krost</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>/brand/fischer</t>
+  </si>
+  <si>
+    <t>Fein</t>
+  </si>
+  <si>
+    <t>/brand/fein</t>
+  </si>
+  <si>
+    <t>Atlas Copco</t>
+  </si>
+  <si>
+    <t>/brand/atlas-copco</t>
+  </si>
+  <si>
+    <t>Starrett</t>
+  </si>
+  <si>
+    <t>/brand/starrett</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>/brand/kennedy</t>
+  </si>
+  <si>
+    <t>JK Files</t>
+  </si>
+  <si>
+    <t>/brand/jk-files</t>
+  </si>
+  <si>
+    <t>KPT Industries</t>
+  </si>
+  <si>
+    <t>/brand/kpt-industries</t>
+  </si>
+  <si>
+    <t>Endico</t>
+  </si>
+  <si>
+    <t>/brand/endico</t>
+  </si>
+  <si>
+    <t>Ralliwolf</t>
+  </si>
+  <si>
+    <t>/brand/ralliwolf</t>
+  </si>
+  <si>
+    <t>ReNew</t>
+  </si>
+  <si>
+    <t>/brand/renew-power</t>
+  </si>
+  <si>
+    <t>Panasonic Solar</t>
+  </si>
+  <si>
+    <t>/brand/panasonic-solar</t>
+  </si>
+  <si>
+    <t>Amaron Solar</t>
+  </si>
+  <si>
+    <t>/brand/amaron-solar</t>
+  </si>
+  <si>
+    <t>Saatvik Solar</t>
+  </si>
+  <si>
+    <t>/brand/saatvik-solar</t>
+  </si>
+  <si>
+    <t>RenewSys</t>
+  </si>
+  <si>
+    <t>/brand/renewsys</t>
+  </si>
+  <si>
+    <t>Patanjali Solar</t>
+  </si>
+  <si>
+    <t>/brand/patanjali-solar</t>
+  </si>
+  <si>
+    <t>Solis Solar</t>
+  </si>
+  <si>
+    <t>/brand/solis-solar</t>
+  </si>
+  <si>
+    <t>Eibenstock</t>
+  </si>
+  <si>
+    <t>/brand/eibenstock</t>
+  </si>
+  <si>
+    <t>Echo</t>
+  </si>
+  <si>
+    <t>/brand/echo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,9 +666,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,7 +694,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -105,13 +702,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,44 +1066,2015 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+    </row>
+    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
